--- a/tests/data/20260603_Experiment_solution-layer.xlsx
+++ b/tests/data/20260603_Experiment_solution-layer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Desktop-PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\root\nomad-distro-dev\packages\nomad-hysprint\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A7A44E-F4D4-424D-BC6F-30750CB030EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9CACD3-A138-452E-AF4C-53E148F7057B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24180" yWindow="2412" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28944" yWindow="3144" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiment Data" sheetId="1" r:id="rId1"/>
